--- a/data/raw/인천 25년/항공통계상세조회(노선) (1).xlsx
+++ b/data/raw/인천 25년/항공통계상세조회(노선) (1).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="575">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>37303</t>
-  </si>
-  <si>
-    <t>6557510</t>
-  </si>
-  <si>
-    <t>321806</t>
+    <t>18658</t>
+  </si>
+  <si>
+    <t>3421003</t>
+  </si>
+  <si>
+    <t>163885</t>
   </si>
   <si>
     <t>인천(ICN)</t>
@@ -53,1864 +53,1690 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>2088</t>
-  </si>
-  <si>
-    <t>394207</t>
-  </si>
-  <si>
-    <t>8574</t>
+    <t>1043</t>
+  </si>
+  <si>
+    <t>204613</t>
+  </si>
+  <si>
+    <t>4181</t>
   </si>
   <si>
     <t>고마스(KMQ)</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>1692</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>과달라하라(GDL)</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>괌(GUM)</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>32044</t>
+  </si>
+  <si>
+    <t>563</t>
+  </si>
+  <si>
+    <t>광저우(CAN)</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>27531</t>
+  </si>
+  <si>
+    <t>2718</t>
+  </si>
+  <si>
+    <t>구마모도(KMJ)</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>12119</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>17088</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>나가사키(NGS)</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>2655</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>나고야(NGO)</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>45755</t>
+  </si>
+  <si>
+    <t>1600</t>
+  </si>
+  <si>
+    <t>나트랑캄란(CXR)</t>
+  </si>
+  <si>
+    <t>489</t>
+  </si>
+  <si>
+    <t>87046</t>
+  </si>
+  <si>
+    <t>901</t>
+  </si>
+  <si>
+    <t>난징(NKG)</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>12206</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>난퉁(NTG)</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>누르술탄 나자르바예프(NQZ)</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>986</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>뉴왁(EWR)</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>7436</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>뉴욕 JFK(JFK)</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>31427</t>
+  </si>
+  <si>
+    <t>3815</t>
+  </si>
+  <si>
+    <t>니이가타(KIJ)</t>
+  </si>
+  <si>
+    <t>1990</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>다가마스(TAK)</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>11207</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>다낭(DAD)</t>
+  </si>
+  <si>
+    <t>513</t>
+  </si>
+  <si>
+    <t>102485</t>
+  </si>
+  <si>
+    <t>1375</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>9838</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>다카(DAC)</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>897</t>
+  </si>
+  <si>
+    <t>달라스(DFW)</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>15746</t>
+  </si>
+  <si>
+    <t>2821</t>
+  </si>
+  <si>
+    <t>달랏(DLI)</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>4559</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>대구(TAE)</t>
+  </si>
+  <si>
+    <t>2338</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>대련(DLC)</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>22962</t>
+  </si>
+  <si>
+    <t>491</t>
+  </si>
+  <si>
+    <t>덴파사(DPS)</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>27226</t>
+  </si>
+  <si>
+    <t>638</t>
+  </si>
+  <si>
+    <t>델리(DEL)</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>8253</t>
+  </si>
+  <si>
+    <t>637</t>
+  </si>
+  <si>
+    <t>도쿄 나리타(NRT)</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>214125</t>
+  </si>
+  <si>
+    <t>7948</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>15215</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>도쿠시마(TKS)</t>
+  </si>
+  <si>
+    <t>1875</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>도하(DOH)</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>13262</t>
+  </si>
+  <si>
+    <t>1888</t>
+  </si>
+  <si>
+    <t>돈무앙(DMK)</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>13483</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>두바이(DXB)</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>24877</t>
+  </si>
+  <si>
+    <t>1409</t>
+  </si>
+  <si>
+    <t>디트로이트(DTW)</t>
+  </si>
+  <si>
+    <t>8190</t>
+  </si>
+  <si>
+    <t>566</t>
+  </si>
+  <si>
+    <t>따이쭝(RMQ)</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>14792</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>라스베가스(LAS)</t>
+  </si>
+  <si>
+    <t>11016</t>
+  </si>
+  <si>
+    <t>655</t>
+  </si>
+  <si>
+    <t>라이프치히(LEJ)</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>랑군(RGN)</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>3324</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>런던히드로(LHR)</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>14903</t>
+  </si>
+  <si>
+    <t>1349</t>
+  </si>
+  <si>
+    <t>로마 파우미치노(FCO)</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>13834</t>
+  </si>
+  <si>
+    <t>460</t>
+  </si>
+  <si>
+    <t>로스앤젤레스(LAX)</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>56196</t>
+  </si>
+  <si>
+    <t>10592</t>
+  </si>
+  <si>
+    <t>루이즈빌(SDF)</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>룩셈부르크(LUX)</t>
+  </si>
+  <si>
+    <t>804</t>
+  </si>
+  <si>
+    <t>리스본(LIS)</t>
+  </si>
+  <si>
+    <t>3523</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>마나스(FRU)</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>828</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>마닐라(MNL)</t>
+  </si>
+  <si>
+    <t>385</t>
+  </si>
+  <si>
+    <t>93701</t>
+  </si>
+  <si>
+    <t>3544</t>
+  </si>
+  <si>
+    <t>마드리드(MAD)</t>
+  </si>
+  <si>
     <t>26</t>
   </si>
   <si>
-    <t>3282</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>과달라하라(GDL)</t>
+    <t>4301</t>
+  </si>
+  <si>
+    <t>776</t>
+  </si>
+  <si>
+    <t>마이애미(MIA)</t>
+  </si>
+  <si>
+    <t>829</t>
+  </si>
+  <si>
+    <t>마즈야마(MYJ)</t>
+  </si>
+  <si>
+    <t>10108</t>
+  </si>
+  <si>
+    <t>마카오(MFM)</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>19326</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>멕시코(MEX)</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>5833</t>
+  </si>
+  <si>
+    <t>393</t>
+  </si>
+  <si>
+    <t>멜버른 툴라마린(MEL)</t>
+  </si>
+  <si>
+    <t>2781</t>
+  </si>
+  <si>
+    <t>멤피스(MEM)</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>무단지앙(MDG)</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>2842</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>뮌헨(MUC)</t>
+  </si>
+  <si>
+    <t>7346</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>미네아폴리스(MSP)</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>944</t>
-  </si>
-  <si>
-    <t>괌(GUM)</t>
-  </si>
-  <si>
-    <t>325</t>
-  </si>
-  <si>
-    <t>61373</t>
-  </si>
-  <si>
-    <t>959</t>
-  </si>
-  <si>
-    <t>광저우(CAN)</t>
-  </si>
-  <si>
-    <t>460</t>
-  </si>
-  <si>
-    <t>56863</t>
-  </si>
-  <si>
-    <t>10325</t>
-  </si>
-  <si>
-    <t>구마모도(KMJ)</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
-    <t>22758</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>359</t>
-  </si>
-  <si>
-    <t>35105</t>
-  </si>
-  <si>
-    <t>716</t>
-  </si>
-  <si>
-    <t>나가사키(NGS)</t>
+    <t>7658</t>
+  </si>
+  <si>
+    <t>미와사키(KMI)</t>
+  </si>
+  <si>
+    <t>4431</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>밀라노(MXP)</t>
+  </si>
+  <si>
+    <t>4907</t>
+  </si>
+  <si>
+    <t>1638</t>
+  </si>
+  <si>
+    <t>바르샤바(WAW)</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>3531</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>바르셀로나(BCN)</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>10229</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>바탐(BTH)</t>
+  </si>
+  <si>
+    <t>999</t>
+  </si>
+  <si>
+    <t>반다르세리베가완(BWN)</t>
+  </si>
+  <si>
+    <t>1427</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>방콕(BKK)</t>
+  </si>
+  <si>
+    <t>509</t>
+  </si>
+  <si>
+    <t>138434</t>
+  </si>
+  <si>
+    <t>5202</t>
+  </si>
+  <si>
+    <t>뱅쿠버(YVR)</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>22682</t>
+  </si>
+  <si>
+    <t>1329</t>
+  </si>
+  <si>
+    <t>보스톤(BOS)</t>
+  </si>
+  <si>
+    <t>7522</t>
+  </si>
+  <si>
+    <t>633</t>
+  </si>
+  <si>
+    <t>부다페스트(BUD)</t>
+  </si>
+  <si>
+    <t>5243</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>39978</t>
+  </si>
+  <si>
+    <t>834</t>
+  </si>
+  <si>
+    <t>브라코프스(VCP)</t>
+  </si>
+  <si>
+    <t>브로츠와프(WRO)</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>브뤼셀(BRU)</t>
+  </si>
+  <si>
+    <t>브리스번(BNE)</t>
+  </si>
+  <si>
+    <t>8999</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>비엔나(VIE)</t>
+  </si>
+  <si>
+    <t>3402</t>
+  </si>
+  <si>
+    <t>1785</t>
+  </si>
+  <si>
+    <t>비엔티안(VTE)</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>21901</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>사가(HSG)</t>
+  </si>
+  <si>
+    <t>2841</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>사이판(SPN)</t>
+  </si>
+  <si>
+    <t>13151</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>산야(SYX)</t>
+  </si>
+  <si>
+    <t>1230</t>
+  </si>
+  <si>
+    <t>삿보로(치토세)(CTS)</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>72392</t>
+  </si>
+  <si>
+    <t>792</t>
+  </si>
+  <si>
+    <t>샌프란시스코(SFO)</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>41820</t>
+  </si>
+  <si>
+    <t>3056</t>
+  </si>
+  <si>
+    <t>샤먼(XMN)</t>
+  </si>
+  <si>
+    <t>8202</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>샤자르(SHJ)</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>세부(CEB)</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>44344</t>
+  </si>
+  <si>
+    <t>876</t>
+  </si>
+  <si>
+    <t>센다이(SDJ)</t>
+  </si>
+  <si>
+    <t>3599</t>
+  </si>
+  <si>
+    <t>센젠(SZX)</t>
+  </si>
+  <si>
+    <t>20129</t>
+  </si>
+  <si>
+    <t>1089</t>
+  </si>
+  <si>
+    <t>쉬지아쭈앙(석가장)(SJW)</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>스텐스테드(STN)</t>
+  </si>
+  <si>
+    <t>462</t>
+  </si>
+  <si>
+    <t>시드니(SYD)</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>42093</t>
+  </si>
+  <si>
+    <t>1654</t>
+  </si>
+  <si>
+    <t>시라하마(SHM)</t>
+  </si>
+  <si>
+    <t>466</t>
+  </si>
+  <si>
+    <t>시모지시마(SHI)</t>
+  </si>
+  <si>
+    <t>3024</t>
+  </si>
+  <si>
+    <t>시안(XIY)</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>7113</t>
+  </si>
+  <si>
+    <t>시애틀(SEA)</t>
+  </si>
+  <si>
+    <t>25630</t>
+  </si>
+  <si>
+    <t>1303</t>
+  </si>
+  <si>
+    <t>시즈오카(FSZ)</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>7642</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>시카고 록퍼드(RFD)</t>
+  </si>
+  <si>
+    <t>시카고(ORD)</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>7751</t>
+  </si>
+  <si>
+    <t>8109</t>
+  </si>
+  <si>
+    <t>신시내티(CVG)</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>1362</t>
+  </si>
+  <si>
+    <t>심양(SHE)</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>24798</t>
+  </si>
+  <si>
+    <t>473</t>
+  </si>
+  <si>
+    <t>싱가폴(SIN)</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>99689</t>
+  </si>
+  <si>
+    <t>5325</t>
+  </si>
+  <si>
+    <t>씨엠립 앙코르(SAI)</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>7909</t>
+  </si>
+  <si>
+    <t>아디스아바바(ADD)</t>
+  </si>
+  <si>
+    <t>3335</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>아사이까와(AKJ)</t>
+  </si>
+  <si>
+    <t>2541</t>
+  </si>
+  <si>
+    <t>아쉬가바트(ASB)</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>아오모리(AOJ)</t>
+  </si>
+  <si>
+    <t>2027</t>
+  </si>
+  <si>
+    <t>아틀란타(ATL)</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>25624</t>
+  </si>
+  <si>
+    <t>2368</t>
+  </si>
+  <si>
+    <t>알마아타(ALA)</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>5514</t>
+  </si>
+  <si>
+    <t>327</t>
+  </si>
+  <si>
+    <t>암스텔담(AMS)</t>
+  </si>
+  <si>
+    <t>10715</t>
+  </si>
+  <si>
+    <t>1737</t>
+  </si>
+  <si>
+    <t>앵커리지(ANC)</t>
+  </si>
+  <si>
+    <t>2478</t>
+  </si>
+  <si>
+    <t>양저우타이저우(YTY)</t>
+  </si>
+  <si>
+    <t>1217</t>
+  </si>
+  <si>
+    <t>어저우화후(EHU)</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>연길(YNJ)</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>22792</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>연대(YNT)</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>13516</t>
+  </si>
+  <si>
+    <t>839</t>
+  </si>
+  <si>
+    <t>염성(YNZ)</t>
+  </si>
+  <si>
+    <t>703</t>
+  </si>
+  <si>
+    <t>오까야마(OKJ)</t>
+  </si>
+  <si>
+    <t>2409</t>
+  </si>
+  <si>
+    <t>오끼나와(OKA)</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>40985</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>오슬로(OSL)</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>오이다(OIT)</t>
+  </si>
+  <si>
+    <t>4541</t>
+  </si>
+  <si>
+    <t>오크랜드(미)(OAK)</t>
+  </si>
+  <si>
+    <t>오클랜드(AKL)</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>12107</t>
+  </si>
+  <si>
+    <t>543</t>
+  </si>
+  <si>
+    <t>요나고(YGJ)</t>
+  </si>
+  <si>
+    <t>2818</t>
+  </si>
+  <si>
+    <t>우베(UBJ)</t>
+  </si>
+  <si>
+    <t>1999</t>
+  </si>
+  <si>
+    <t>우시샤우팡(WUX)</t>
+  </si>
+  <si>
+    <t>5674</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>우한(무한)(WUH)</t>
+  </si>
+  <si>
+    <t>3340</t>
+  </si>
+  <si>
+    <t>우후(WHA)</t>
+  </si>
+  <si>
+    <t>울란바토르(신)(UBN)</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>22315</t>
+  </si>
+  <si>
+    <t>840</t>
+  </si>
+  <si>
+    <t>워싱턴 덜레스(IAD)</t>
+  </si>
+  <si>
+    <t>7718</t>
+  </si>
+  <si>
+    <t>622</t>
+  </si>
+  <si>
+    <t>원저우(WNZ)</t>
+  </si>
+  <si>
+    <t>2528</t>
+  </si>
+  <si>
+    <t>웨이하이(WEH)</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>8938</t>
+  </si>
+  <si>
+    <t>479</t>
+  </si>
+  <si>
+    <t>이스탄불(IST)</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>22267</t>
+  </si>
+  <si>
+    <t>2208</t>
+  </si>
+  <si>
+    <t>인디아나폴리스(IND)</t>
+  </si>
+  <si>
+    <t>자무쓰(JMU)</t>
+  </si>
+  <si>
+    <t>764</t>
+  </si>
+  <si>
+    <t>자이드(AUH)</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>11860</t>
+  </si>
+  <si>
+    <t>787</t>
+  </si>
+  <si>
+    <t>자카르타(CGK)</t>
+  </si>
+  <si>
+    <t>24794</t>
+  </si>
+  <si>
+    <t>1386</t>
+  </si>
+  <si>
+    <t>장가계(대용)(DYG)</t>
+  </si>
+  <si>
+    <t>2643</t>
+  </si>
+  <si>
+    <t>장춘(CGQ)</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>9785</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>정저우(CGO)</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>573</t>
+  </si>
+  <si>
+    <t>지난(TNA)</t>
+  </si>
+  <si>
+    <t>7811</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>창사(CSX)</t>
+  </si>
+  <si>
+    <t>5373</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>천진(TSN)</t>
+  </si>
+  <si>
+    <t>11880</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>청도(TAO)</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>61885</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>청두(CTU)</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>총킹(중경)(CKG)</t>
+  </si>
+  <si>
+    <t>2483</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>충하이보아오(BAR)</t>
+  </si>
+  <si>
+    <t>취리히(ZRH)</t>
+  </si>
+  <si>
+    <t>치앙마이(CNX)</t>
+  </si>
+  <si>
+    <t>39829</t>
+  </si>
+  <si>
+    <t>581</t>
+  </si>
+  <si>
+    <t>카고시마(KOJ)</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>7021</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>17949</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>카이로(CAI)</t>
+  </si>
+  <si>
+    <t>2530</t>
+  </si>
+  <si>
+    <t>카투만두(KTM)</t>
+  </si>
+  <si>
+    <t>3290</t>
+  </si>
+  <si>
+    <t>칼리보(KLO)</t>
+  </si>
+  <si>
+    <t>14839</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>코타키나발루(BKI)</t>
+  </si>
+  <si>
+    <t>24888</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>콜롬보(CMB)</t>
+  </si>
+  <si>
+    <t>2767</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>쿠알라룸푸르(KUL)</t>
+  </si>
+  <si>
+    <t>43339</t>
+  </si>
+  <si>
+    <t>1881</t>
+  </si>
+  <si>
+    <t>쿤밍(KMG)</t>
+  </si>
+  <si>
+    <t>3747</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>퀼른(CGN)</t>
+  </si>
+  <si>
+    <t>클라크 필드(CRK)</t>
+  </si>
+  <si>
+    <t>21459</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>키타큐슈(KKJ)</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>8832</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>타쉬켄트(TAS)</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>11456</t>
+  </si>
+  <si>
+    <t>562</t>
+  </si>
+  <si>
+    <t>타이페이(TPE)</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>106527</t>
+  </si>
+  <si>
+    <t>3828</t>
+  </si>
+  <si>
+    <t>타크빌라란(TAG)</t>
+  </si>
+  <si>
+    <t>25419</t>
+  </si>
+  <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>텐푸(TFU)</t>
+  </si>
+  <si>
+    <t>4995</t>
+  </si>
+  <si>
+    <t>토론토(YYZ)</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>16838</t>
+  </si>
+  <si>
+    <t>1848</t>
+  </si>
+  <si>
+    <t>파리 샤를드골(CDG)</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>27438</t>
+  </si>
+  <si>
+    <t>1434</t>
+  </si>
+  <si>
+    <t>페낭(PEN)</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>푸동(PVG)</t>
+  </si>
+  <si>
+    <t>528</t>
+  </si>
+  <si>
+    <t>76663</t>
+  </si>
+  <si>
+    <t>7759</t>
+  </si>
+  <si>
+    <t>푸조우(FOC)</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
-    <t>4712</t>
+    <t>3408</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
-    <t>나고야(NGO)</t>
-  </si>
-  <si>
-    <t>513</t>
-  </si>
-  <si>
-    <t>85424</t>
-  </si>
-  <si>
-    <t>2588</t>
-  </si>
-  <si>
-    <t>나트랑캄란(CXR)</t>
-  </si>
-  <si>
-    <t>976</t>
-  </si>
-  <si>
-    <t>170801</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>난징(NKG)</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
-    <t>24121</t>
-  </si>
-  <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>난퉁(NTG)</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>누르술탄 나자르바예프(NQZ)</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>뉴왁(EWR)</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>13226</t>
-  </si>
-  <si>
-    <t>뉴욕 JFK(JFK)</t>
-  </si>
-  <si>
-    <t>273</t>
-  </si>
-  <si>
-    <t>60265</t>
-  </si>
-  <si>
-    <t>5835</t>
-  </si>
-  <si>
-    <t>니이가타(KIJ)</t>
-  </si>
-  <si>
-    <t>3594</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>다가마스(TAK)</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>21294</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>다낭(DAD)</t>
-  </si>
-  <si>
-    <t>1027</t>
-  </si>
-  <si>
-    <t>196161</t>
-  </si>
-  <si>
-    <t>3247</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>19550</t>
-  </si>
-  <si>
-    <t>402</t>
-  </si>
-  <si>
-    <t>다카(DAC)</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>1522</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>달라스(DFW)</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>29424</t>
-  </si>
-  <si>
-    <t>3870</t>
-  </si>
-  <si>
-    <t>달랏(DLI)</t>
+    <t>푸켓(HKT)</t>
+  </si>
+  <si>
+    <t>13018</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>푸쿡(PQC)</t>
+  </si>
+  <si>
+    <t>54748</t>
+  </si>
+  <si>
+    <t>프라하(PRG)</t>
+  </si>
+  <si>
+    <t>3505</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>프랑크푸르트(FRA)</t>
+  </si>
+  <si>
+    <t>19884</t>
+  </si>
+  <si>
+    <t>3830</t>
+  </si>
+  <si>
+    <t>프롬펜(PNH)</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>18063</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>하노이(HAN)</t>
+  </si>
+  <si>
+    <t>434</t>
+  </si>
+  <si>
+    <t>77188</t>
+  </si>
+  <si>
+    <t>8359</t>
+  </si>
+  <si>
+    <t>하얼빈(HRB)</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>14056</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>하이커우(HAK)</t>
+  </si>
+  <si>
+    <t>2360</t>
+  </si>
+  <si>
+    <t>하이퐁(HPH)</t>
+  </si>
+  <si>
+    <t>6230</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>항조우(HGH)</t>
+  </si>
+  <si>
+    <t>14367</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>허폐(HFE)</t>
+  </si>
+  <si>
+    <t>1669</t>
+  </si>
+  <si>
+    <t>헌츠빌(HSV)</t>
+  </si>
+  <si>
+    <t>헤이다르 알리예프(GYD)</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>695</t>
+  </si>
+  <si>
+    <t>헬싱키(HEL)</t>
+  </si>
+  <si>
+    <t>7039</t>
+  </si>
+  <si>
+    <t>487</t>
+  </si>
+  <si>
+    <t>호놀룰루(HNL)</t>
   </si>
   <si>
     <t>74</t>
   </si>
   <si>
-    <t>8426</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>대구(TAE)</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>4749</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>대련(DLC)</t>
-  </si>
-  <si>
-    <t>288</t>
-  </si>
-  <si>
-    <t>43955</t>
-  </si>
-  <si>
-    <t>1171</t>
-  </si>
-  <si>
-    <t>덴파사(DPS)</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>52288</t>
-  </si>
-  <si>
-    <t>1069</t>
-  </si>
-  <si>
-    <t>델리(DEL)</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>15416</t>
-  </si>
-  <si>
-    <t>975</t>
-  </si>
-  <si>
-    <t>도쿄 나리타(NRT)</t>
-  </si>
-  <si>
-    <t>2199</t>
-  </si>
-  <si>
-    <t>408744</t>
-  </si>
-  <si>
-    <t>15849</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>187</t>
-  </si>
-  <si>
-    <t>29675</t>
-  </si>
-  <si>
-    <t>도쿠시마(TKS)</t>
-  </si>
-  <si>
-    <t>3629</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>도하(DOH)</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>23589</t>
-  </si>
-  <si>
-    <t>3293</t>
-  </si>
-  <si>
-    <t>돈무앙(DMK)</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>25167</t>
-  </si>
-  <si>
-    <t>423</t>
-  </si>
-  <si>
-    <t>두바이(DXB)</t>
-  </si>
-  <si>
-    <t>152</t>
-  </si>
-  <si>
-    <t>46985</t>
-  </si>
-  <si>
-    <t>2272</t>
-  </si>
-  <si>
-    <t>디트로이트(DTW)</t>
-  </si>
-  <si>
-    <t>15140</t>
-  </si>
-  <si>
-    <t>777</t>
-  </si>
-  <si>
-    <t>따이쭝(RMQ)</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>29852</t>
-  </si>
-  <si>
-    <t>367</t>
-  </si>
-  <si>
-    <t>라스베가스(LAS)</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>20445</t>
-  </si>
-  <si>
-    <t>900</t>
-  </si>
-  <si>
-    <t>라이프치히(LEJ)</t>
-  </si>
-  <si>
-    <t>2047</t>
-  </si>
-  <si>
-    <t>랑군(RGN)</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>6439</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>런던히드로(LHR)</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>26808</t>
-  </si>
-  <si>
-    <t>2233</t>
-  </si>
-  <si>
-    <t>로마 파우미치노(FCO)</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>27033</t>
-  </si>
-  <si>
-    <t>885</t>
-  </si>
-  <si>
-    <t>로스앤젤레스(LAX)</t>
-  </si>
-  <si>
-    <t>501</t>
-  </si>
-  <si>
-    <t>105740</t>
-  </si>
-  <si>
-    <t>14514</t>
-  </si>
-  <si>
-    <t>루이즈빌(SDF)</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>룩셈부르크(LUX)</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>1206</t>
-  </si>
-  <si>
-    <t>리마(LIM)</t>
-  </si>
-  <si>
-    <t>243</t>
-  </si>
-  <si>
-    <t>리스본(LIS)</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>6486</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>마나스(FRU)</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>1410</t>
-  </si>
-  <si>
-    <t>마닐라(MNL)</t>
-  </si>
-  <si>
-    <t>771</t>
-  </si>
-  <si>
-    <t>176954</t>
-  </si>
-  <si>
-    <t>5944</t>
-  </si>
-  <si>
-    <t>마드리드(MAD)</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>8444</t>
-  </si>
-  <si>
-    <t>1786</t>
-  </si>
-  <si>
-    <t>마이애미(MIA)</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>856</t>
-  </si>
-  <si>
-    <t>마즈야마(MYJ)</t>
-  </si>
-  <si>
-    <t>19191</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>마카오(MFM)</t>
-  </si>
-  <si>
-    <t>278</t>
-  </si>
-  <si>
-    <t>38723</t>
-  </si>
-  <si>
-    <t>459</t>
-  </si>
-  <si>
-    <t>마쿵(MZG)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>멕시코(MEX)</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>8301</t>
-  </si>
-  <si>
-    <t>멜버른 툴라마린(MEL)</t>
-  </si>
-  <si>
-    <t>5288</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>멤피스(MEM)</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>365</t>
-  </si>
-  <si>
-    <t>몬테레이(MTY)</t>
-  </si>
-  <si>
-    <t>1880</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>무단지앙(MDG)</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>4867</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>뮌헨(MUC)</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>13987</t>
-  </si>
-  <si>
-    <t>732</t>
-  </si>
-  <si>
-    <t>미네아폴리스(MSP)</t>
-  </si>
-  <si>
-    <t>14734</t>
-  </si>
-  <si>
-    <t>733</t>
-  </si>
-  <si>
-    <t>미와사키(KMI)</t>
-  </si>
-  <si>
-    <t>8155</t>
-  </si>
-  <si>
-    <t>149</t>
-  </si>
-  <si>
-    <t>밀라노(MXP)</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>9003</t>
-  </si>
-  <si>
-    <t>3426</t>
-  </si>
-  <si>
-    <t>바르샤바(WAW)</t>
-  </si>
-  <si>
-    <t>6684</t>
-  </si>
-  <si>
-    <t>413</t>
-  </si>
-  <si>
-    <t>바르셀로나(BCN)</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>20067</t>
-  </si>
-  <si>
-    <t>585</t>
-  </si>
-  <si>
-    <t>바탐(BTH)</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>반다르세리베가완(BWN)</t>
-  </si>
-  <si>
-    <t>2580</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>방콕(BKK)</t>
-  </si>
-  <si>
-    <t>1018</t>
-  </si>
-  <si>
-    <t>266013</t>
-  </si>
-  <si>
-    <t>10437</t>
-  </si>
-  <si>
-    <t>뱅쿠버(YVR)</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>43106</t>
-  </si>
-  <si>
-    <t>2373</t>
-  </si>
-  <si>
-    <t>보스톤(BOS)</t>
-  </si>
-  <si>
-    <t>14520</t>
-  </si>
-  <si>
-    <t>908</t>
-  </si>
-  <si>
-    <t>부다페스트(BUD)</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>9862</t>
-  </si>
-  <si>
-    <t>511</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>548</t>
-  </si>
-  <si>
-    <t>82292</t>
-  </si>
-  <si>
-    <t>2050</t>
-  </si>
-  <si>
-    <t>브라코프스(VCP)</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>브로츠와프(WRO)</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>1738</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>브뤼셀(BRU)</t>
-  </si>
-  <si>
-    <t>588</t>
-  </si>
-  <si>
-    <t>브리스번(BNE)</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>16575</t>
-  </si>
-  <si>
-    <t>553</t>
-  </si>
-  <si>
-    <t>비엔나(VIE)</t>
-  </si>
-  <si>
-    <t>6219</t>
-  </si>
-  <si>
-    <t>1877</t>
-  </si>
-  <si>
-    <t>비엔티안(VTE)</t>
-  </si>
-  <si>
-    <t>284</t>
-  </si>
-  <si>
-    <t>43283</t>
-  </si>
-  <si>
-    <t>580</t>
-  </si>
-  <si>
-    <t>사가(HSG)</t>
-  </si>
-  <si>
-    <t>5403</t>
-  </si>
-  <si>
-    <t>사르고사(ZAZ)</t>
-  </si>
-  <si>
-    <t>사이판(SPN)</t>
-  </si>
-  <si>
-    <t>25741</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>산야(SYX)</t>
-  </si>
-  <si>
-    <t>2600</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>산티아고(SCL)</t>
-  </si>
-  <si>
-    <t>삿보로(치토세)(CTS)</t>
-  </si>
-  <si>
-    <t>666</t>
-  </si>
-  <si>
-    <t>143308</t>
-  </si>
-  <si>
-    <t>1793</t>
-  </si>
-  <si>
-    <t>샌프란시스코(SFO)</t>
-  </si>
-  <si>
-    <t>76368</t>
-  </si>
-  <si>
-    <t>6100</t>
-  </si>
-  <si>
-    <t>샤먼(XMN)</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>16557</t>
-  </si>
-  <si>
-    <t>338</t>
-  </si>
-  <si>
-    <t>샤자르(SHJ)</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>세부(CEB)</t>
-  </si>
-  <si>
-    <t>433</t>
-  </si>
-  <si>
-    <t>84531</t>
-  </si>
-  <si>
-    <t>1541</t>
-  </si>
-  <si>
-    <t>센다이(SDJ)</t>
-  </si>
-  <si>
-    <t>6732</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>센젠(SZX)</t>
-  </si>
-  <si>
-    <t>42730</t>
-  </si>
-  <si>
-    <t>2749</t>
-  </si>
-  <si>
-    <t>쉬지아쭈앙(석가장)(SJW)</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>583</t>
-  </si>
-  <si>
-    <t>스텐스테드(STN)</t>
-  </si>
-  <si>
-    <t>462</t>
-  </si>
-  <si>
-    <t>시드니(SYD)</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>76773</t>
-  </si>
-  <si>
-    <t>2523</t>
-  </si>
-  <si>
-    <t>시라하마(SHM)</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>779</t>
-  </si>
-  <si>
-    <t>시모지시마(SHI)</t>
-  </si>
-  <si>
-    <t>5578</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>시안(XIY)</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>13846</t>
-  </si>
-  <si>
-    <t>682</t>
-  </si>
-  <si>
-    <t>시애틀(SEA)</t>
-  </si>
-  <si>
-    <t>257</t>
-  </si>
-  <si>
-    <t>48207</t>
-  </si>
-  <si>
-    <t>3746</t>
-  </si>
-  <si>
-    <t>시즈오카(FSZ)</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>14276</t>
-  </si>
-  <si>
-    <t>134</t>
-  </si>
-  <si>
-    <t>시카고 록퍼드(RFD)</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>시카고(ORD)</t>
-  </si>
-  <si>
-    <t>463</t>
-  </si>
-  <si>
-    <t>14636</t>
-  </si>
-  <si>
-    <t>9720</t>
-  </si>
-  <si>
-    <t>신시내티(CVG)</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>2680</t>
-  </si>
-  <si>
-    <t>심양(SHE)</t>
-  </si>
-  <si>
-    <t>286</t>
-  </si>
-  <si>
-    <t>44633</t>
-  </si>
-  <si>
-    <t>871</t>
-  </si>
-  <si>
-    <t>싱가폴(SIN)</t>
-  </si>
-  <si>
-    <t>787</t>
-  </si>
-  <si>
-    <t>179189</t>
-  </si>
-  <si>
-    <t>9821</t>
-  </si>
-  <si>
-    <t>씨엠립 앙코르(SAI)</t>
-  </si>
-  <si>
-    <t>15289</t>
-  </si>
-  <si>
-    <t>아디스아바바(ADD)</t>
-  </si>
-  <si>
-    <t>6128</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>아사이까와(AKJ)</t>
-  </si>
-  <si>
-    <t>4793</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>아쉬가바트(ASB)</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>아오모리(AOJ)</t>
-  </si>
-  <si>
-    <t>4012</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>아틀란타(ATL)</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>49121</t>
-  </si>
-  <si>
-    <t>3701</t>
-  </si>
-  <si>
-    <t>알마아타(ALA)</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>9814</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>암스텔담(AMS)</t>
-  </si>
-  <si>
-    <t>20065</t>
-  </si>
-  <si>
-    <t>3821</t>
-  </si>
-  <si>
-    <t>앵커리지(ANC)</t>
-  </si>
-  <si>
-    <t>3561</t>
-  </si>
-  <si>
-    <t>양저우타이저우(YTY)</t>
-  </si>
-  <si>
-    <t>2403</t>
-  </si>
-  <si>
-    <t>어저우화후(EHU)</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>324</t>
-  </si>
-  <si>
-    <t>에드먼튼(YEG)</t>
-  </si>
-  <si>
-    <t>연길(YNJ)</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>43189</t>
-  </si>
-  <si>
-    <t>670</t>
-  </si>
-  <si>
-    <t>연대(YNT)</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t>24359</t>
-  </si>
-  <si>
-    <t>2382</t>
-  </si>
-  <si>
-    <t>염성(YNZ)</t>
-  </si>
-  <si>
-    <t>1441</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>오까야마(OKJ)</t>
-  </si>
-  <si>
-    <t>4630</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>오끼나와(OKA)</t>
-  </si>
-  <si>
-    <t>391</t>
-  </si>
-  <si>
-    <t>78052</t>
-  </si>
-  <si>
-    <t>845</t>
-  </si>
-  <si>
-    <t>오슬로(OSL)</t>
-  </si>
-  <si>
-    <t>1761</t>
-  </si>
-  <si>
-    <t>오이다(OIT)</t>
-  </si>
-  <si>
-    <t>8525</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>오크랜드(미)(OAK)</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>오클랜드(AKL)</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>21940</t>
-  </si>
-  <si>
-    <t>990</t>
-  </si>
-  <si>
-    <t>온타리오(ONT)</t>
-  </si>
-  <si>
-    <t>요나고(YGJ)</t>
-  </si>
-  <si>
-    <t>5407</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>우베(UBJ)</t>
-  </si>
-  <si>
-    <t>3827</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>우시샤우팡(WUX)</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>11578</t>
-  </si>
-  <si>
-    <t>737</t>
-  </si>
-  <si>
-    <t>우한(무한)(WUH)</t>
-  </si>
-  <si>
-    <t>6765</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>우후(WHA)</t>
-  </si>
-  <si>
-    <t>347</t>
-  </si>
-  <si>
-    <t>울란바토르(신)(UBN)</t>
-  </si>
-  <si>
-    <t>245</t>
-  </si>
-  <si>
-    <t>41120</t>
-  </si>
-  <si>
-    <t>1223</t>
-  </si>
-  <si>
-    <t>워싱턴 덜레스(IAD)</t>
-  </si>
-  <si>
-    <t>14635</t>
-  </si>
-  <si>
-    <t>955</t>
-  </si>
-  <si>
-    <t>원저우(WNZ)</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>5223</t>
-  </si>
-  <si>
-    <t>745</t>
-  </si>
-  <si>
-    <t>웨이하이(WEH)</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>17485</t>
-  </si>
-  <si>
-    <t>1254</t>
-  </si>
-  <si>
-    <t>이스탄불(IST)</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>41849</t>
-  </si>
-  <si>
-    <t>3768</t>
-  </si>
-  <si>
-    <t>인디아나폴리스(IND)</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>자무쓰(JMU)</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>자이드(AUH)</t>
-  </si>
-  <si>
-    <t>21559</t>
-  </si>
-  <si>
-    <t>1407</t>
-  </si>
-  <si>
-    <t>자카르타(CGK)</t>
-  </si>
-  <si>
-    <t>44629</t>
-  </si>
-  <si>
-    <t>2396</t>
-  </si>
-  <si>
-    <t>장가계(대용)(DYG)</t>
-  </si>
-  <si>
-    <t>5310</t>
-  </si>
-  <si>
-    <t>장춘(CGQ)</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>16904</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>정저우(CGO)</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>8357</t>
-  </si>
-  <si>
-    <t>1628</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>지난(TNA)</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>15653</t>
-  </si>
-  <si>
-    <t>창사(CSX)</t>
-  </si>
-  <si>
-    <t>10583</t>
-  </si>
-  <si>
-    <t>천진(TSN)</t>
-  </si>
-  <si>
-    <t>283</t>
-  </si>
-  <si>
-    <t>24131</t>
-  </si>
-  <si>
-    <t>2788</t>
-  </si>
-  <si>
-    <t>청도(TAO)</t>
-  </si>
-  <si>
-    <t>904</t>
-  </si>
-  <si>
-    <t>121451</t>
-  </si>
-  <si>
-    <t>2943</t>
-  </si>
-  <si>
-    <t>청두(CTU)</t>
-  </si>
-  <si>
-    <t>279</t>
-  </si>
-  <si>
-    <t>총킹(중경)(CKG)</t>
-  </si>
-  <si>
-    <t>5075</t>
-  </si>
-  <si>
-    <t>287</t>
-  </si>
-  <si>
-    <t>충하이보아오(BAR)</t>
-  </si>
-  <si>
-    <t>472</t>
-  </si>
-  <si>
-    <t>취리히(ZRH)</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>치앙마이(CNX)</t>
-  </si>
-  <si>
-    <t>75695</t>
-  </si>
-  <si>
-    <t>1161</t>
-  </si>
-  <si>
-    <t>카고시마(KOJ)</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>13194</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>36319</t>
-  </si>
-  <si>
-    <t>546</t>
-  </si>
-  <si>
-    <t>카이로(CAI)</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>5249</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>카투만두(KTM)</t>
-  </si>
-  <si>
-    <t>6484</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>칼리보(KLO)</t>
-  </si>
-  <si>
-    <t>28562</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>코타키나발루(BKI)</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>49341</t>
-  </si>
-  <si>
-    <t>544</t>
-  </si>
-  <si>
-    <t>콜롬보(CMB)</t>
-  </si>
-  <si>
-    <t>5002</t>
-  </si>
-  <si>
-    <t>296</t>
-  </si>
-  <si>
-    <t>쿠알라룸푸르(KUL)</t>
-  </si>
-  <si>
-    <t>329</t>
-  </si>
-  <si>
-    <t>79688</t>
-  </si>
-  <si>
-    <t>3258</t>
-  </si>
-  <si>
-    <t>쿤밍(KMG)</t>
-  </si>
-  <si>
-    <t>7050</t>
-  </si>
-  <si>
-    <t>퀼른(CGN)</t>
-  </si>
-  <si>
-    <t>클라크 필드(CRK)</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>39467</t>
-  </si>
-  <si>
-    <t>660</t>
-  </si>
-  <si>
-    <t>키타큐슈(KKJ)</t>
-  </si>
-  <si>
-    <t>16258</t>
-  </si>
-  <si>
-    <t>437</t>
-  </si>
-  <si>
-    <t>타쉬켄트(TAS)</t>
-  </si>
-  <si>
-    <t>21440</t>
-  </si>
-  <si>
-    <t>868</t>
-  </si>
-  <si>
-    <t>타이페이(TPE)</t>
-  </si>
-  <si>
-    <t>751</t>
-  </si>
-  <si>
-    <t>216275</t>
-  </si>
-  <si>
-    <t>7226</t>
-  </si>
-  <si>
-    <t>타크빌라란(TAG)</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>50268</t>
-  </si>
-  <si>
-    <t>522</t>
-  </si>
-  <si>
-    <t>텐푸(TFU)</t>
-  </si>
-  <si>
-    <t>9935</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>토론토(YYZ)</t>
-  </si>
-  <si>
-    <t>32598</t>
-  </si>
-  <si>
-    <t>2894</t>
-  </si>
-  <si>
-    <t>파리 샤를드골(CDG)</t>
-  </si>
-  <si>
-    <t>51521</t>
-  </si>
-  <si>
-    <t>3252</t>
-  </si>
-  <si>
-    <t>페낭(PEN)</t>
-  </si>
-  <si>
-    <t>1288</t>
-  </si>
-  <si>
-    <t>푸동(PVG)</t>
-  </si>
-  <si>
-    <t>1055</t>
-  </si>
-  <si>
-    <t>157105</t>
-  </si>
-  <si>
-    <t>18351</t>
-  </si>
-  <si>
-    <t>푸조우(FOC)</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>6701</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>푸켓(HKT)</t>
-  </si>
-  <si>
-    <t>26101</t>
-  </si>
-  <si>
-    <t>427</t>
-  </si>
-  <si>
-    <t>푸쿡(PQC)</t>
-  </si>
-  <si>
-    <t>495</t>
-  </si>
-  <si>
-    <t>108623</t>
-  </si>
-  <si>
-    <t>1214</t>
-  </si>
-  <si>
-    <t>프라하(PRG)</t>
-  </si>
-  <si>
-    <t>6509</t>
-  </si>
-  <si>
-    <t>프랑크푸르트(FRA)</t>
-  </si>
-  <si>
-    <t>36410</t>
-  </si>
-  <si>
-    <t>7181</t>
-  </si>
-  <si>
-    <t>프롬펜(PNH)</t>
-  </si>
-  <si>
-    <t>33613</t>
-  </si>
-  <si>
-    <t>1046</t>
-  </si>
-  <si>
-    <t>하노이(HAN)</t>
-  </si>
-  <si>
-    <t>870</t>
-  </si>
-  <si>
-    <t>140646</t>
-  </si>
-  <si>
-    <t>15400</t>
-  </si>
-  <si>
-    <t>하얼빈(HRB)</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>24935</t>
-  </si>
-  <si>
-    <t>383</t>
-  </si>
-  <si>
-    <t>하이커우(HAK)</t>
-  </si>
-  <si>
-    <t>4704</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>하이퐁(HPH)</t>
-  </si>
-  <si>
-    <t>11572</t>
-  </si>
-  <si>
-    <t>266</t>
-  </si>
-  <si>
-    <t>항조우(HGH)</t>
-  </si>
-  <si>
-    <t>30300</t>
-  </si>
-  <si>
-    <t>516</t>
-  </si>
-  <si>
-    <t>허폐(HFE)</t>
-  </si>
-  <si>
-    <t>3390</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>헌츠빌(HSV)</t>
-  </si>
-  <si>
-    <t>헤이다르 알리예프(GYD)</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>1050</t>
-  </si>
-  <si>
-    <t>헬리팍스(YHZ)</t>
-  </si>
-  <si>
-    <t>804</t>
-  </si>
-  <si>
-    <t>헬싱키(HEL)</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>12825</t>
-  </si>
-  <si>
-    <t>1124</t>
-  </si>
-  <si>
-    <t>호놀룰루(HNL)</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>40933</t>
-  </si>
-  <si>
-    <t>1771</t>
+    <t>22094</t>
+  </si>
+  <si>
+    <t>1233</t>
   </si>
   <si>
     <t>호치민(SGN)</t>
   </si>
   <si>
-    <t>708</t>
-  </si>
-  <si>
-    <t>155099</t>
-  </si>
-  <si>
-    <t>6900</t>
+    <t>84757</t>
+  </si>
+  <si>
+    <t>3205</t>
   </si>
   <si>
     <t>홍콩(HKG)</t>
   </si>
   <si>
-    <t>1477</t>
-  </si>
-  <si>
-    <t>253302</t>
-  </si>
-  <si>
-    <t>23001</t>
+    <t>744</t>
+  </si>
+  <si>
+    <t>128496</t>
+  </si>
+  <si>
+    <t>8066</t>
   </si>
   <si>
     <t>후쿠오카(FUK)</t>
   </si>
   <si>
-    <t>1423</t>
-  </si>
-  <si>
-    <t>293971</t>
-  </si>
-  <si>
-    <t>3620</t>
+    <t>711</t>
+  </si>
+  <si>
+    <t>151241</t>
+  </si>
+  <si>
+    <t>1657</t>
   </si>
   <si>
     <t>히로시마(HIJ)</t>
   </si>
   <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>13956</t>
-  </si>
-  <si>
-    <t>123</t>
+    <t>7490</t>
   </si>
 </sst>
 </file>
@@ -1961,7 +1787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F192"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="30"/>
   <sheetData>
     <row r="1">
@@ -2261,7 +2087,7 @@
         <v>61</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -2272,16 +2098,16 @@
         <v>11</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -2292,16 +2118,16 @@
         <v>11</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
@@ -2312,16 +2138,16 @@
         <v>11</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>17</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
@@ -2332,16 +2158,16 @@
         <v>11</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20">
@@ -2352,16 +2178,16 @@
         <v>11</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
@@ -2372,16 +2198,16 @@
         <v>11</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22">
@@ -2392,16 +2218,16 @@
         <v>11</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23">
@@ -2412,16 +2238,16 @@
         <v>11</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24">
@@ -2432,16 +2258,16 @@
         <v>11</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25">
@@ -2452,10 +2278,10 @@
         <v>11</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>97</v>
@@ -2561,7 +2387,7 @@
         <v>117</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>37</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31">
@@ -2572,16 +2398,16 @@
         <v>11</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>17</v>
       </c>
       <c r="E31" t="s" s="0">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32">
@@ -2592,16 +2418,16 @@
         <v>11</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E32" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33">
@@ -2612,16 +2438,16 @@
         <v>11</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E33" t="s" s="0">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34">
@@ -2632,16 +2458,16 @@
         <v>11</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E34" t="s" s="0">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35">
@@ -2652,16 +2478,16 @@
         <v>11</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="E35" t="s" s="0">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36">
@@ -2672,16 +2498,16 @@
         <v>11</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E36" t="s" s="0">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37">
@@ -2692,10 +2518,10 @@
         <v>11</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>142</v>
@@ -2715,13 +2541,13 @@
         <v>144</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>43</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>22</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39">
@@ -2732,16 +2558,16 @@
         <v>11</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40">
@@ -2752,16 +2578,16 @@
         <v>11</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41">
@@ -2772,16 +2598,16 @@
         <v>11</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42">
@@ -2792,16 +2618,16 @@
         <v>11</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E42" t="s" s="0">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F42" t="s" s="0">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43">
@@ -2812,10 +2638,10 @@
         <v>11</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>22</v>
@@ -2832,10 +2658,10 @@
         <v>11</v>
       </c>
       <c r="C44" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="D44" t="s" s="0">
         <v>164</v>
-      </c>
-      <c r="D44" t="s" s="0">
-        <v>165</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>22</v>
@@ -2855,13 +2681,13 @@
         <v>167</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E45" t="s" s="0">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="F45" t="s" s="0">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46">
@@ -2872,16 +2698,16 @@
         <v>11</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E46" t="s" s="0">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" t="s" s="0">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47">
@@ -2892,16 +2718,16 @@
         <v>11</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E47" t="s" s="0">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" t="s" s="0">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48">
@@ -2912,16 +2738,16 @@
         <v>11</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49">
@@ -2932,13 +2758,13 @@
         <v>11</v>
       </c>
       <c r="C49" t="s" s="0">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>182</v>
+        <v>22</v>
       </c>
       <c r="F49" t="s" s="0">
         <v>183</v>
@@ -2955,13 +2781,13 @@
         <v>184</v>
       </c>
       <c r="D50" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="E50" t="s" s="0">
         <v>185</v>
       </c>
-      <c r="E50" t="s" s="0">
-        <v>22</v>
-      </c>
       <c r="F50" t="s" s="0">
-        <v>186</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51">
@@ -2972,10 +2798,10 @@
         <v>11</v>
       </c>
       <c r="C51" t="s" s="0">
+        <v>186</v>
+      </c>
+      <c r="D51" t="s" s="0">
         <v>187</v>
-      </c>
-      <c r="D51" t="s" s="0">
-        <v>73</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>188</v>
@@ -3015,13 +2841,13 @@
         <v>194</v>
       </c>
       <c r="D53" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="E53" t="s" s="0">
         <v>195</v>
       </c>
-      <c r="E53" t="s" s="0">
-        <v>196</v>
-      </c>
       <c r="F53" t="s" s="0">
-        <v>197</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54">
@@ -3032,16 +2858,16 @@
         <v>11</v>
       </c>
       <c r="C54" t="s" s="0">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E54" t="s" s="0">
-        <v>200</v>
+        <v>22</v>
       </c>
       <c r="F54" t="s" s="0">
-        <v>193</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55">
@@ -3052,16 +2878,16 @@
         <v>11</v>
       </c>
       <c r="C55" t="s" s="0">
+        <v>198</v>
+      </c>
+      <c r="D55" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="E55" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="F55" t="s" s="0">
         <v>201</v>
-      </c>
-      <c r="D55" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="E55" t="s" s="0">
-        <v>202</v>
-      </c>
-      <c r="F55" t="s" s="0">
-        <v>203</v>
       </c>
     </row>
     <row r="56">
@@ -3072,16 +2898,16 @@
         <v>11</v>
       </c>
       <c r="C56" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="D56" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="E56" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="F56" t="s" s="0">
         <v>204</v>
-      </c>
-      <c r="D56" t="s" s="0">
-        <v>205</v>
-      </c>
-      <c r="E56" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="F56" t="s" s="0">
-        <v>206</v>
       </c>
     </row>
     <row r="57">
@@ -3092,16 +2918,16 @@
         <v>11</v>
       </c>
       <c r="C57" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="D57" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="E57" t="s" s="0">
         <v>207</v>
       </c>
-      <c r="D57" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="E57" t="s" s="0">
-        <v>208</v>
-      </c>
       <c r="F57" t="s" s="0">
-        <v>209</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58">
@@ -3112,16 +2938,16 @@
         <v>11</v>
       </c>
       <c r="C58" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="D58" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E58" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="F58" t="s" s="0">
         <v>210</v>
-      </c>
-      <c r="D58" t="s" s="0">
-        <v>211</v>
-      </c>
-      <c r="E58" t="s" s="0">
-        <v>212</v>
-      </c>
-      <c r="F58" t="s" s="0">
-        <v>213</v>
       </c>
     </row>
     <row r="59">
@@ -3132,16 +2958,16 @@
         <v>11</v>
       </c>
       <c r="C59" t="s" s="0">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>215</v>
+        <v>98</v>
       </c>
       <c r="E59" t="s" s="0">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F59" t="s" s="0">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="60">
@@ -3152,16 +2978,16 @@
         <v>11</v>
       </c>
       <c r="C60" t="s" s="0">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>163</v>
+        <v>215</v>
       </c>
       <c r="E60" t="s" s="0">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F60" t="s" s="0">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61">
@@ -3172,16 +2998,16 @@
         <v>11</v>
       </c>
       <c r="C61" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="D61" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="E61" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="F61" t="s" s="0">
         <v>221</v>
-      </c>
-      <c r="D61" t="s" s="0">
-        <v>96</v>
-      </c>
-      <c r="E61" t="s" s="0">
-        <v>222</v>
-      </c>
-      <c r="F61" t="s" s="0">
-        <v>223</v>
       </c>
     </row>
     <row r="62">
@@ -3192,16 +3018,16 @@
         <v>11</v>
       </c>
       <c r="C62" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>225</v>
+        <v>60</v>
       </c>
       <c r="E62" t="s" s="0">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F62" t="s" s="0">
-        <v>227</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63">
@@ -3212,16 +3038,16 @@
         <v>11</v>
       </c>
       <c r="C63" t="s" s="0">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>185</v>
+        <v>17</v>
       </c>
       <c r="E63" t="s" s="0">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F63" t="s" s="0">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64">
@@ -3232,16 +3058,16 @@
         <v>11</v>
       </c>
       <c r="C64" t="s" s="0">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E64" t="s" s="0">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F64" t="s" s="0">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="65">
@@ -3252,16 +3078,16 @@
         <v>11</v>
       </c>
       <c r="C65" t="s" s="0">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>60</v>
+        <v>232</v>
       </c>
       <c r="E65" t="s" s="0">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F65" t="s" s="0">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="66">
@@ -3272,16 +3098,16 @@
         <v>11</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="E66" t="s" s="0">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F66" t="s" s="0">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="67">
@@ -3292,16 +3118,16 @@
         <v>11</v>
       </c>
       <c r="C67" t="s" s="0">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="E67" t="s" s="0">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F67" t="s" s="0">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="68">
@@ -3312,16 +3138,16 @@
         <v>11</v>
       </c>
       <c r="C68" t="s" s="0">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E68" t="s" s="0">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F68" t="s" s="0">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="69">
@@ -3332,16 +3158,16 @@
         <v>11</v>
       </c>
       <c r="C69" t="s" s="0">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="E69" t="s" s="0">
-        <v>250</v>
+        <v>22</v>
       </c>
       <c r="F69" t="s" s="0">
-        <v>251</v>
+        <v>140</v>
       </c>
     </row>
     <row r="70">
@@ -3352,16 +3178,16 @@
         <v>11</v>
       </c>
       <c r="C70" t="s" s="0">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E70" t="s" s="0">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="F70" t="s" s="0">
-        <v>255</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71">
@@ -3372,16 +3198,16 @@
         <v>11</v>
       </c>
       <c r="C71" t="s" s="0">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>257</v>
+        <v>17</v>
       </c>
       <c r="E71" t="s" s="0">
-        <v>258</v>
+        <v>22</v>
       </c>
       <c r="F71" t="s" s="0">
-        <v>259</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72">
@@ -3392,16 +3218,16 @@
         <v>11</v>
       </c>
       <c r="C72" t="s" s="0">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>174</v>
+        <v>43</v>
       </c>
       <c r="E72" t="s" s="0">
-        <v>22</v>
+        <v>251</v>
       </c>
       <c r="F72" t="s" s="0">
-        <v>261</v>
+        <v>252</v>
       </c>
     </row>
     <row r="73">
@@ -3412,16 +3238,16 @@
         <v>11</v>
       </c>
       <c r="C73" t="s" s="0">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="E73" t="s" s="0">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F73" t="s" s="0">
-        <v>265</v>
+        <v>255</v>
       </c>
     </row>
     <row r="74">
@@ -3432,16 +3258,16 @@
         <v>11</v>
       </c>
       <c r="C74" t="s" s="0">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>17</v>
+        <v>257</v>
       </c>
       <c r="E74" t="s" s="0">
-        <v>22</v>
+        <v>258</v>
       </c>
       <c r="F74" t="s" s="0">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="75">
@@ -3452,16 +3278,16 @@
         <v>11</v>
       </c>
       <c r="C75" t="s" s="0">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>269</v>
+        <v>19</v>
       </c>
       <c r="E75" t="s" s="0">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F75" t="s" s="0">
-        <v>271</v>
+        <v>262</v>
       </c>
     </row>
     <row r="76">
@@ -3472,16 +3298,16 @@
         <v>11</v>
       </c>
       <c r="C76" t="s" s="0">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="E76" t="s" s="0">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="F76" t="s" s="0">
-        <v>274</v>
+        <v>265</v>
       </c>
     </row>
     <row r="77">
@@ -3492,16 +3318,16 @@
         <v>11</v>
       </c>
       <c r="C77" t="s" s="0">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>276</v>
+        <v>60</v>
       </c>
       <c r="E77" t="s" s="0">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="F77" t="s" s="0">
-        <v>278</v>
+        <v>215</v>
       </c>
     </row>
     <row r="78">
@@ -3512,16 +3338,16 @@
         <v>11</v>
       </c>
       <c r="C78" t="s" s="0">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>19</v>
+        <v>269</v>
       </c>
       <c r="E78" t="s" s="0">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="F78" t="s" s="0">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="79">
@@ -3532,16 +3358,16 @@
         <v>11</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>7</v>
+        <v>273</v>
       </c>
       <c r="E79" t="s" s="0">
-        <v>22</v>
+        <v>274</v>
       </c>
       <c r="F79" t="s" s="0">
-        <v>17</v>
+        <v>275</v>
       </c>
     </row>
     <row r="80">
@@ -3552,16 +3378,16 @@
         <v>11</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="E80" t="s" s="0">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F80" t="s" s="0">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="81">
@@ -3572,16 +3398,16 @@
         <v>11</v>
       </c>
       <c r="C81" t="s" s="0">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="E81" t="s" s="0">
-        <v>286</v>
+        <v>22</v>
       </c>
       <c r="F81" t="s" s="0">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
     <row r="82">
@@ -3592,16 +3418,16 @@
         <v>11</v>
       </c>
       <c r="C82" t="s" s="0">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>7</v>
+        <v>282</v>
       </c>
       <c r="E82" t="s" s="0">
-        <v>22</v>
+        <v>283</v>
       </c>
       <c r="F82" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="83">
@@ -3612,16 +3438,16 @@
         <v>11</v>
       </c>
       <c r="C83" t="s" s="0">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>290</v>
+        <v>199</v>
       </c>
       <c r="E83" t="s" s="0">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="F83" t="s" s="0">
-        <v>292</v>
+        <v>123</v>
       </c>
     </row>
     <row r="84">
@@ -3632,16 +3458,16 @@
         <v>11</v>
       </c>
       <c r="C84" t="s" s="0">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>37</v>
+        <v>257</v>
       </c>
       <c r="E84" t="s" s="0">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F84" t="s" s="0">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="85">
@@ -3652,16 +3478,16 @@
         <v>11</v>
       </c>
       <c r="C85" t="s" s="0">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E85" t="s" s="0">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F85" t="s" s="0">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="86">
@@ -3672,7 +3498,7 @@
         <v>11</v>
       </c>
       <c r="C86" t="s" s="0">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D86" t="s" s="0">
         <v>7</v>
@@ -3681,7 +3507,7 @@
         <v>22</v>
       </c>
       <c r="F86" t="s" s="0">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="87">
@@ -3692,16 +3518,16 @@
         <v>11</v>
       </c>
       <c r="C87" t="s" s="0">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E87" t="s" s="0">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="F87" t="s" s="0">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="88">
@@ -3712,16 +3538,16 @@
         <v>11</v>
       </c>
       <c r="C88" t="s" s="0">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="E88" t="s" s="0">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F88" t="s" s="0">
-        <v>308</v>
+        <v>247</v>
       </c>
     </row>
     <row r="89">
@@ -3732,16 +3558,16 @@
         <v>11</v>
       </c>
       <c r="C89" t="s" s="0">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>276</v>
+        <v>199</v>
       </c>
       <c r="E89" t="s" s="0">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F89" t="s" s="0">
-        <v>311</v>
+        <v>226</v>
       </c>
     </row>
     <row r="90">
@@ -3752,16 +3578,16 @@
         <v>11</v>
       </c>
       <c r="C90" t="s" s="0">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="E90" t="s" s="0">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F90" t="s" s="0">
-        <v>84</v>
+        <v>158</v>
       </c>
     </row>
     <row r="91">
@@ -3772,16 +3598,16 @@
         <v>11</v>
       </c>
       <c r="C91" t="s" s="0">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="E91" t="s" s="0">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="F91" t="s" s="0">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="92">
@@ -3792,16 +3618,16 @@
         <v>11</v>
       </c>
       <c r="C92" t="s" s="0">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="E92" t="s" s="0">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="F92" t="s" s="0">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="93">
@@ -3812,16 +3638,16 @@
         <v>11</v>
       </c>
       <c r="C93" t="s" s="0">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>322</v>
+        <v>19</v>
       </c>
       <c r="E93" t="s" s="0">
-        <v>323</v>
+        <v>22</v>
       </c>
       <c r="F93" t="s" s="0">
-        <v>263</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94">
@@ -3832,16 +3658,16 @@
         <v>11</v>
       </c>
       <c r="C94" t="s" s="0">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>211</v>
+        <v>316</v>
       </c>
       <c r="E94" t="s" s="0">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="F94" t="s" s="0">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="95">
@@ -3852,16 +3678,16 @@
         <v>11</v>
       </c>
       <c r="C95" t="s" s="0">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E95" t="s" s="0">
-        <v>329</v>
+        <v>22</v>
       </c>
       <c r="F95" t="s" s="0">
-        <v>330</v>
+        <v>321</v>
       </c>
     </row>
     <row r="96">
@@ -3872,16 +3698,16 @@
         <v>11</v>
       </c>
       <c r="C96" t="s" s="0">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="E96" t="s" s="0">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="F96" t="s" s="0">
-        <v>334</v>
+        <v>325</v>
       </c>
     </row>
     <row r="97">
@@ -3892,16 +3718,16 @@
         <v>11</v>
       </c>
       <c r="C97" t="s" s="0">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E97" t="s" s="0">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="F97" t="s" s="0">
-        <v>338</v>
+        <v>329</v>
       </c>
     </row>
     <row r="98">
@@ -3912,16 +3738,16 @@
         <v>11</v>
       </c>
       <c r="C98" t="s" s="0">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="E98" t="s" s="0">
-        <v>22</v>
+        <v>332</v>
       </c>
       <c r="F98" t="s" s="0">
-        <v>211</v>
+        <v>89</v>
       </c>
     </row>
     <row r="99">
@@ -3932,16 +3758,16 @@
         <v>11</v>
       </c>
       <c r="C99" t="s" s="0">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>342</v>
+        <v>179</v>
       </c>
       <c r="E99" t="s" s="0">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="F99" t="s" s="0">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="100">
@@ -3952,16 +3778,16 @@
         <v>11</v>
       </c>
       <c r="C100" t="s" s="0">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>346</v>
+        <v>41</v>
       </c>
       <c r="E100" t="s" s="0">
-        <v>22</v>
+        <v>337</v>
       </c>
       <c r="F100" t="s" s="0">
-        <v>347</v>
+        <v>145</v>
       </c>
     </row>
     <row r="101">
@@ -3972,16 +3798,16 @@
         <v>11</v>
       </c>
       <c r="C101" t="s" s="0">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>349</v>
+        <v>293</v>
       </c>
       <c r="E101" t="s" s="0">
-        <v>350</v>
+        <v>22</v>
       </c>
       <c r="F101" t="s" s="0">
-        <v>351</v>
+        <v>339</v>
       </c>
     </row>
     <row r="102">
@@ -3992,16 +3818,16 @@
         <v>11</v>
       </c>
       <c r="C102" t="s" s="0">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>353</v>
+        <v>21</v>
       </c>
       <c r="E102" t="s" s="0">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="F102" t="s" s="0">
-        <v>355</v>
+        <v>199</v>
       </c>
     </row>
     <row r="103">
@@ -4012,16 +3838,16 @@
         <v>11</v>
       </c>
       <c r="C103" t="s" s="0">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>86</v>
+        <v>343</v>
       </c>
       <c r="E103" t="s" s="0">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="F103" t="s" s="0">
-        <v>223</v>
+        <v>345</v>
       </c>
     </row>
     <row r="104">
@@ -4032,16 +3858,16 @@
         <v>11</v>
       </c>
       <c r="C104" t="s" s="0">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>181</v>
+        <v>347</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>360</v>
+        <v>349</v>
       </c>
     </row>
     <row r="105">
@@ -4052,16 +3878,16 @@
         <v>11</v>
       </c>
       <c r="C105" t="s" s="0">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>41</v>
+        <v>156</v>
       </c>
       <c r="E105" t="s" s="0">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="F105" t="s" s="0">
-        <v>363</v>
+        <v>352</v>
       </c>
     </row>
     <row r="106">
@@ -4072,16 +3898,16 @@
         <v>11</v>
       </c>
       <c r="C106" t="s" s="0">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>365</v>
+        <v>280</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>22</v>
       </c>
       <c r="F106" t="s" s="0">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="107">
@@ -4092,16 +3918,16 @@
         <v>11</v>
       </c>
       <c r="C107" t="s" s="0">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="E107" t="s" s="0">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="F107" t="s" s="0">
-        <v>369</v>
+        <v>215</v>
       </c>
     </row>
     <row r="108">
@@ -4112,16 +3938,16 @@
         <v>11</v>
       </c>
       <c r="C108" t="s" s="0">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>371</v>
+        <v>19</v>
       </c>
       <c r="E108" t="s" s="0">
-        <v>372</v>
+        <v>22</v>
       </c>
       <c r="F108" t="s" s="0">
-        <v>373</v>
+        <v>358</v>
       </c>
     </row>
     <row r="109">
@@ -4132,16 +3958,16 @@
         <v>11</v>
       </c>
       <c r="C109" t="s" s="0">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="E109" t="s" s="0">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="F109" t="s" s="0">
-        <v>377</v>
+        <v>362</v>
       </c>
     </row>
     <row r="110">
@@ -4152,16 +3978,16 @@
         <v>11</v>
       </c>
       <c r="C110" t="s" s="0">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>98</v>
+        <v>364</v>
       </c>
       <c r="E110" t="s" s="0">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="F110" t="s" s="0">
-        <v>380</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111">
@@ -4172,16 +3998,16 @@
         <v>11</v>
       </c>
       <c r="C111" t="s" s="0">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>332</v>
+        <v>179</v>
       </c>
       <c r="E111" t="s" s="0">
-        <v>22</v>
+        <v>368</v>
       </c>
       <c r="F111" t="s" s="0">
-        <v>382</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112">
@@ -4192,16 +4018,16 @@
         <v>11</v>
       </c>
       <c r="C112" t="s" s="0">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="E112" t="s" s="0">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="F112" t="s" s="0">
-        <v>17</v>
+        <v>148</v>
       </c>
     </row>
     <row r="113">
@@ -4212,16 +4038,16 @@
         <v>11</v>
       </c>
       <c r="C113" t="s" s="0">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>22</v>
+        <v>373</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>387</v>
+        <v>374</v>
       </c>
     </row>
     <row r="114">
@@ -4232,16 +4058,16 @@
         <v>11</v>
       </c>
       <c r="C114" t="s" s="0">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="E114" t="s" s="0">
         <v>22</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>22</v>
+        <v>376</v>
       </c>
     </row>
     <row r="115">
@@ -4252,16 +4078,16 @@
         <v>11</v>
       </c>
       <c r="C115" t="s" s="0">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>390</v>
+        <v>43</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>392</v>
+        <v>226</v>
       </c>
     </row>
     <row r="116">
@@ -4272,16 +4098,16 @@
         <v>11</v>
       </c>
       <c r="C116" t="s" s="0">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>394</v>
+        <v>7</v>
       </c>
       <c r="E116" t="s" s="0">
-        <v>395</v>
+        <v>22</v>
       </c>
       <c r="F116" t="s" s="0">
-        <v>396</v>
+        <v>22</v>
       </c>
     </row>
     <row r="117">
@@ -4292,16 +4118,16 @@
         <v>11</v>
       </c>
       <c r="C117" t="s" s="0">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>215</v>
+        <v>381</v>
       </c>
       <c r="E117" t="s" s="0">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="F117" t="s" s="0">
-        <v>399</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118">
@@ -4312,16 +4138,16 @@
         <v>11</v>
       </c>
       <c r="C118" t="s" s="0">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>19</v>
+        <v>173</v>
       </c>
       <c r="E118" t="s" s="0">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="F118" t="s" s="0">
-        <v>402</v>
+        <v>262</v>
       </c>
     </row>
     <row r="119">
@@ -4332,16 +4158,16 @@
         <v>11</v>
       </c>
       <c r="C119" t="s" s="0">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>404</v>
+        <v>121</v>
       </c>
       <c r="E119" t="s" s="0">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="F119" t="s" s="0">
-        <v>406</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120">
@@ -4352,16 +4178,16 @@
         <v>11</v>
       </c>
       <c r="C120" t="s" s="0">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>287</v>
+        <v>89</v>
       </c>
       <c r="E120" t="s" s="0">
-        <v>22</v>
+        <v>389</v>
       </c>
       <c r="F120" t="s" s="0">
-        <v>408</v>
+        <v>390</v>
       </c>
     </row>
     <row r="121">
@@ -4372,16 +4198,16 @@
         <v>11</v>
       </c>
       <c r="C121" t="s" s="0">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="D121" t="s" s="0">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="E121" t="s" s="0">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="F121" t="s" s="0">
-        <v>411</v>
+        <v>116</v>
       </c>
     </row>
     <row r="122">
@@ -4392,16 +4218,16 @@
         <v>11</v>
       </c>
       <c r="C122" t="s" s="0">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>413</v>
+        <v>62</v>
       </c>
       <c r="E122" t="s" s="0">
         <v>22</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>22</v>
+        <v>291</v>
       </c>
     </row>
     <row r="123">
@@ -4412,16 +4238,16 @@
         <v>11</v>
       </c>
       <c r="C123" t="s" s="0">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="E123" t="s" s="0">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>417</v>
+        <v>397</v>
       </c>
     </row>
     <row r="124">
@@ -4432,16 +4258,16 @@
         <v>11</v>
       </c>
       <c r="C124" t="s" s="0">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="E124" t="s" s="0">
-        <v>22</v>
+        <v>399</v>
       </c>
       <c r="F124" t="s" s="0">
-        <v>22</v>
+        <v>400</v>
       </c>
     </row>
     <row r="125">
@@ -4452,16 +4278,16 @@
         <v>11</v>
       </c>
       <c r="C125" t="s" s="0">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="D125" t="s" s="0">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="E125" t="s" s="0">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="F125" t="s" s="0">
-        <v>421</v>
+        <v>339</v>
       </c>
     </row>
     <row r="126">
@@ -4472,16 +4298,16 @@
         <v>11</v>
       </c>
       <c r="C126" t="s" s="0">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="D126" t="s" s="0">
-        <v>340</v>
+        <v>404</v>
       </c>
       <c r="E126" t="s" s="0">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="F126" t="s" s="0">
-        <v>424</v>
+        <v>406</v>
       </c>
     </row>
     <row r="127">
@@ -4492,16 +4318,16 @@
         <v>11</v>
       </c>
       <c r="C127" t="s" s="0">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="D127" t="s" s="0">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="E127" t="s" s="0">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="F127" t="s" s="0">
-        <v>428</v>
+        <v>410</v>
       </c>
     </row>
     <row r="128">
@@ -4512,16 +4338,16 @@
         <v>11</v>
       </c>
       <c r="C128" t="s" s="0">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="D128" t="s" s="0">
-        <v>19</v>
+        <v>311</v>
       </c>
       <c r="E128" t="s" s="0">
-        <v>430</v>
+        <v>22</v>
       </c>
       <c r="F128" t="s" s="0">
-        <v>431</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129">
@@ -4532,16 +4358,16 @@
         <v>11</v>
       </c>
       <c r="C129" t="s" s="0">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="D129" t="s" s="0">
-        <v>421</v>
+        <v>247</v>
       </c>
       <c r="E129" t="s" s="0">
-        <v>22</v>
+        <v>413</v>
       </c>
       <c r="F129" t="s" s="0">
-        <v>433</v>
+        <v>164</v>
       </c>
     </row>
     <row r="130">
@@ -4552,16 +4378,16 @@
         <v>11</v>
       </c>
       <c r="C130" t="s" s="0">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="D130" t="s" s="0">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="E130" t="s" s="0">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="F130" t="s" s="0">
-        <v>437</v>
+        <v>417</v>
       </c>
     </row>
     <row r="131">
@@ -4572,16 +4398,16 @@
         <v>11</v>
       </c>
       <c r="C131" t="s" s="0">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="D131" t="s" s="0">
-        <v>96</v>
+        <v>305</v>
       </c>
       <c r="E131" t="s" s="0">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="F131" t="s" s="0">
-        <v>440</v>
+        <v>420</v>
       </c>
     </row>
     <row r="132">
@@ -4592,16 +4418,16 @@
         <v>11</v>
       </c>
       <c r="C132" t="s" s="0">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="D132" t="s" s="0">
-        <v>442</v>
+        <v>62</v>
       </c>
       <c r="E132" t="s" s="0">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="F132" t="s" s="0">
-        <v>444</v>
+        <v>73</v>
       </c>
     </row>
     <row r="133">
@@ -4612,16 +4438,16 @@
         <v>11</v>
       </c>
       <c r="C133" t="s" s="0">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="D133" t="s" s="0">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="E133" t="s" s="0">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="F133" t="s" s="0">
-        <v>448</v>
+        <v>426</v>
       </c>
     </row>
     <row r="134">
@@ -4632,16 +4458,16 @@
         <v>11</v>
       </c>
       <c r="C134" t="s" s="0">
-        <v>449</v>
+        <v>427</v>
       </c>
       <c r="D134" t="s" s="0">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="E134" t="s" s="0">
-        <v>451</v>
+        <v>15</v>
       </c>
       <c r="F134" t="s" s="0">
-        <v>452</v>
+        <v>429</v>
       </c>
     </row>
     <row r="135">
@@ -4652,16 +4478,16 @@
         <v>11</v>
       </c>
       <c r="C135" t="s" s="0">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="D135" t="s" s="0">
-        <v>454</v>
+        <v>152</v>
       </c>
       <c r="E135" t="s" s="0">
-        <v>22</v>
+        <v>431</v>
       </c>
       <c r="F135" t="s" s="0">
-        <v>22</v>
+        <v>432</v>
       </c>
     </row>
     <row r="136">
@@ -4672,16 +4498,16 @@
         <v>11</v>
       </c>
       <c r="C136" t="s" s="0">
-        <v>455</v>
+        <v>433</v>
       </c>
       <c r="D136" t="s" s="0">
-        <v>456</v>
+        <v>415</v>
       </c>
       <c r="E136" t="s" s="0">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F136" t="s" s="0">
-        <v>413</v>
+        <v>435</v>
       </c>
     </row>
     <row r="137">
@@ -4692,16 +4518,16 @@
         <v>11</v>
       </c>
       <c r="C137" t="s" s="0">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="D137" t="s" s="0">
-        <v>86</v>
+        <v>257</v>
       </c>
       <c r="E137" t="s" s="0">
-        <v>458</v>
+        <v>437</v>
       </c>
       <c r="F137" t="s" s="0">
-        <v>459</v>
+        <v>438</v>
       </c>
     </row>
     <row r="138">
@@ -4712,16 +4538,16 @@
         <v>11</v>
       </c>
       <c r="C138" t="s" s="0">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="D138" t="s" s="0">
-        <v>328</v>
+        <v>440</v>
       </c>
       <c r="E138" t="s" s="0">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="F138" t="s" s="0">
-        <v>462</v>
+        <v>442</v>
       </c>
     </row>
     <row r="139">
@@ -4732,16 +4558,16 @@
         <v>11</v>
       </c>
       <c r="C139" t="s" s="0">
-        <v>463</v>
+        <v>443</v>
       </c>
       <c r="D139" t="s" s="0">
-        <v>253</v>
+        <v>164</v>
       </c>
       <c r="E139" t="s" s="0">
-        <v>464</v>
+        <v>22</v>
       </c>
       <c r="F139" t="s" s="0">
-        <v>240</v>
+        <v>444</v>
       </c>
     </row>
     <row r="140">
@@ -4752,16 +4578,16 @@
         <v>11</v>
       </c>
       <c r="C140" t="s" s="0">
-        <v>465</v>
+        <v>445</v>
       </c>
       <c r="D140" t="s" s="0">
-        <v>466</v>
+        <v>43</v>
       </c>
       <c r="E140" t="s" s="0">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="F140" t="s" s="0">
-        <v>468</v>
+        <v>447</v>
       </c>
     </row>
     <row r="141">
@@ -4772,16 +4598,16 @@
         <v>11</v>
       </c>
       <c r="C141" t="s" s="0">
-        <v>469</v>
+        <v>448</v>
       </c>
       <c r="D141" t="s" s="0">
-        <v>470</v>
+        <v>293</v>
       </c>
       <c r="E141" t="s" s="0">
-        <v>471</v>
+        <v>189</v>
       </c>
       <c r="F141" t="s" s="0">
-        <v>472</v>
+        <v>291</v>
       </c>
     </row>
     <row r="142">
@@ -4792,16 +4618,16 @@
         <v>11</v>
       </c>
       <c r="C142" t="s" s="0">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="D142" t="s" s="0">
-        <v>263</v>
+        <v>86</v>
       </c>
       <c r="E142" t="s" s="0">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="F142" t="s" s="0">
-        <v>322</v>
+        <v>226</v>
       </c>
     </row>
     <row r="143">
@@ -4812,16 +4638,16 @@
         <v>11</v>
       </c>
       <c r="C143" t="s" s="0">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="D143" t="s" s="0">
-        <v>475</v>
+        <v>84</v>
       </c>
       <c r="E143" t="s" s="0">
-        <v>476</v>
+        <v>451</v>
       </c>
       <c r="F143" t="s" s="0">
-        <v>82</v>
+        <v>452</v>
       </c>
     </row>
     <row r="144">
@@ -4832,16 +4658,16 @@
         <v>11</v>
       </c>
       <c r="C144" t="s" s="0">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="D144" t="s" s="0">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="E144" t="s" s="0">
-        <v>478</v>
+        <v>455</v>
       </c>
       <c r="F144" t="s" s="0">
-        <v>137</v>
+        <v>456</v>
       </c>
     </row>
     <row r="145">
@@ -4852,16 +4678,16 @@
         <v>11</v>
       </c>
       <c r="C145" t="s" s="0">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="D145" t="s" s="0">
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="E145" t="s" s="0">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="F145" t="s" s="0">
-        <v>482</v>
+        <v>459</v>
       </c>
     </row>
     <row r="146">
@@ -4872,16 +4698,16 @@
         <v>11</v>
       </c>
       <c r="C146" t="s" s="0">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="D146" t="s" s="0">
-        <v>484</v>
+        <v>60</v>
       </c>
       <c r="E146" t="s" s="0">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="F146" t="s" s="0">
-        <v>486</v>
+        <v>210</v>
       </c>
     </row>
     <row r="147">
@@ -4892,16 +4718,16 @@
         <v>11</v>
       </c>
       <c r="C147" t="s" s="0">
-        <v>487</v>
+        <v>462</v>
       </c>
       <c r="D147" t="s" s="0">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="E147" t="s" s="0">
-        <v>22</v>
+        <v>463</v>
       </c>
       <c r="F147" t="s" s="0">
-        <v>488</v>
+        <v>372</v>
       </c>
     </row>
     <row r="148">
@@ -4912,16 +4738,16 @@
         <v>11</v>
       </c>
       <c r="C148" t="s" s="0">
-        <v>489</v>
+        <v>464</v>
       </c>
       <c r="D148" t="s" s="0">
-        <v>96</v>
+        <v>376</v>
       </c>
       <c r="E148" t="s" s="0">
-        <v>490</v>
+        <v>465</v>
       </c>
       <c r="F148" t="s" s="0">
-        <v>491</v>
+        <v>466</v>
       </c>
     </row>
     <row r="149">
@@ -4932,16 +4758,16 @@
         <v>11</v>
       </c>
       <c r="C149" t="s" s="0">
-        <v>492</v>
+        <v>467</v>
       </c>
       <c r="D149" t="s" s="0">
-        <v>365</v>
+        <v>466</v>
       </c>
       <c r="E149" t="s" s="0">
-        <v>493</v>
+        <v>468</v>
       </c>
       <c r="F149" t="s" s="0">
-        <v>322</v>
+        <v>469</v>
       </c>
     </row>
     <row r="150">
@@ -4952,16 +4778,16 @@
         <v>11</v>
       </c>
       <c r="C150" t="s" s="0">
-        <v>494</v>
+        <v>470</v>
       </c>
       <c r="D150" t="s" s="0">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="E150" t="s" s="0">
-        <v>22</v>
+        <v>471</v>
       </c>
       <c r="F150" t="s" s="0">
-        <v>495</v>
+        <v>472</v>
       </c>
     </row>
     <row r="151">
@@ -4972,16 +4798,16 @@
         <v>11</v>
       </c>
       <c r="C151" t="s" s="0">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="D151" t="s" s="0">
-        <v>206</v>
+        <v>339</v>
       </c>
       <c r="E151" t="s" s="0">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="F151" t="s" s="0">
-        <v>498</v>
+        <v>475</v>
       </c>
     </row>
     <row r="152">
@@ -4992,16 +4818,16 @@
         <v>11</v>
       </c>
       <c r="C152" t="s" s="0">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="D152" t="s" s="0">
-        <v>500</v>
+        <v>108</v>
       </c>
       <c r="E152" t="s" s="0">
-        <v>501</v>
+        <v>477</v>
       </c>
       <c r="F152" t="s" s="0">
-        <v>502</v>
+        <v>478</v>
       </c>
     </row>
     <row r="153">
@@ -5012,16 +4838,16 @@
         <v>11</v>
       </c>
       <c r="C153" t="s" s="0">
-        <v>503</v>
+        <v>479</v>
       </c>
       <c r="D153" t="s" s="0">
-        <v>504</v>
+        <v>7</v>
       </c>
       <c r="E153" t="s" s="0">
-        <v>505</v>
+        <v>22</v>
       </c>
       <c r="F153" t="s" s="0">
-        <v>506</v>
+        <v>376</v>
       </c>
     </row>
     <row r="154">
@@ -5032,16 +4858,16 @@
         <v>11</v>
       </c>
       <c r="C154" t="s" s="0">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="D154" t="s" s="0">
-        <v>508</v>
+        <v>432</v>
       </c>
       <c r="E154" t="s" s="0">
-        <v>509</v>
+        <v>481</v>
       </c>
       <c r="F154" t="s" s="0">
-        <v>510</v>
+        <v>482</v>
       </c>
     </row>
     <row r="155">
@@ -5052,16 +4878,16 @@
         <v>11</v>
       </c>
       <c r="C155" t="s" s="0">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="D155" t="s" s="0">
-        <v>170</v>
+        <v>484</v>
       </c>
       <c r="E155" t="s" s="0">
-        <v>512</v>
+        <v>485</v>
       </c>
       <c r="F155" t="s" s="0">
-        <v>513</v>
+        <v>486</v>
       </c>
     </row>
     <row r="156">
@@ -5072,16 +4898,16 @@
         <v>11</v>
       </c>
       <c r="C156" t="s" s="0">
-        <v>514</v>
+        <v>487</v>
       </c>
       <c r="D156" t="s" s="0">
-        <v>189</v>
+        <v>488</v>
       </c>
       <c r="E156" t="s" s="0">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="F156" t="s" s="0">
-        <v>516</v>
+        <v>490</v>
       </c>
     </row>
     <row r="157">
@@ -5092,16 +4918,16 @@
         <v>11</v>
       </c>
       <c r="C157" t="s" s="0">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="D157" t="s" s="0">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="E157" t="s" s="0">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="F157" t="s" s="0">
-        <v>520</v>
+        <v>494</v>
       </c>
     </row>
     <row r="158">
@@ -5112,16 +4938,16 @@
         <v>11</v>
       </c>
       <c r="C158" t="s" s="0">
-        <v>521</v>
+        <v>495</v>
       </c>
       <c r="D158" t="s" s="0">
-        <v>57</v>
+        <v>466</v>
       </c>
       <c r="E158" t="s" s="0">
-        <v>522</v>
+        <v>496</v>
       </c>
       <c r="F158" t="s" s="0">
-        <v>523</v>
+        <v>497</v>
       </c>
     </row>
     <row r="159">
@@ -5132,16 +4958,16 @@
         <v>11</v>
       </c>
       <c r="C159" t="s" s="0">
-        <v>524</v>
+        <v>498</v>
       </c>
       <c r="D159" t="s" s="0">
-        <v>525</v>
+        <v>226</v>
       </c>
       <c r="E159" t="s" s="0">
-        <v>526</v>
+        <v>499</v>
       </c>
       <c r="F159" t="s" s="0">
-        <v>527</v>
+        <v>146</v>
       </c>
     </row>
     <row r="160">
@@ -5152,16 +4978,16 @@
         <v>11</v>
       </c>
       <c r="C160" t="s" s="0">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="D160" t="s" s="0">
-        <v>108</v>
+        <v>501</v>
       </c>
       <c r="E160" t="s" s="0">
-        <v>529</v>
+        <v>502</v>
       </c>
       <c r="F160" t="s" s="0">
-        <v>466</v>
+        <v>503</v>
       </c>
     </row>
     <row r="161">
@@ -5172,16 +4998,16 @@
         <v>11</v>
       </c>
       <c r="C161" t="s" s="0">
-        <v>530</v>
+        <v>504</v>
       </c>
       <c r="D161" t="s" s="0">
-        <v>7</v>
+        <v>505</v>
       </c>
       <c r="E161" t="s" s="0">
-        <v>22</v>
+        <v>506</v>
       </c>
       <c r="F161" t="s" s="0">
-        <v>126</v>
+        <v>507</v>
       </c>
     </row>
     <row r="162">
@@ -5192,16 +5018,16 @@
         <v>11</v>
       </c>
       <c r="C162" t="s" s="0">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="D162" t="s" s="0">
-        <v>532</v>
+        <v>164</v>
       </c>
       <c r="E162" t="s" s="0">
-        <v>533</v>
+        <v>22</v>
       </c>
       <c r="F162" t="s" s="0">
-        <v>534</v>
+        <v>509</v>
       </c>
     </row>
     <row r="163">
@@ -5212,16 +5038,16 @@
         <v>11</v>
       </c>
       <c r="C163" t="s" s="0">
-        <v>535</v>
+        <v>510</v>
       </c>
       <c r="D163" t="s" s="0">
-        <v>94</v>
+        <v>511</v>
       </c>
       <c r="E163" t="s" s="0">
-        <v>536</v>
+        <v>512</v>
       </c>
       <c r="F163" t="s" s="0">
-        <v>537</v>
+        <v>513</v>
       </c>
     </row>
     <row r="164">
@@ -5232,16 +5058,16 @@
         <v>11</v>
       </c>
       <c r="C164" t="s" s="0">
-        <v>538</v>
+        <v>514</v>
       </c>
       <c r="D164" t="s" s="0">
-        <v>225</v>
+        <v>515</v>
       </c>
       <c r="E164" t="s" s="0">
-        <v>539</v>
+        <v>516</v>
       </c>
       <c r="F164" t="s" s="0">
-        <v>540</v>
+        <v>517</v>
       </c>
     </row>
     <row r="165">
@@ -5252,16 +5078,16 @@
         <v>11</v>
       </c>
       <c r="C165" t="s" s="0">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="D165" t="s" s="0">
-        <v>542</v>
+        <v>75</v>
       </c>
       <c r="E165" t="s" s="0">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="F165" t="s" s="0">
-        <v>544</v>
+        <v>520</v>
       </c>
     </row>
     <row r="166">
@@ -5272,16 +5098,16 @@
         <v>11</v>
       </c>
       <c r="C166" t="s" s="0">
-        <v>545</v>
+        <v>521</v>
       </c>
       <c r="D166" t="s" s="0">
-        <v>546</v>
+        <v>45</v>
       </c>
       <c r="E166" t="s" s="0">
-        <v>547</v>
+        <v>522</v>
       </c>
       <c r="F166" t="s" s="0">
-        <v>548</v>
+        <v>383</v>
       </c>
     </row>
     <row r="167">
@@ -5292,16 +5118,16 @@
         <v>11</v>
       </c>
       <c r="C167" t="s" s="0">
-        <v>549</v>
+        <v>523</v>
       </c>
       <c r="D167" t="s" s="0">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="E167" t="s" s="0">
-        <v>550</v>
+        <v>524</v>
       </c>
       <c r="F167" t="s" s="0">
-        <v>551</v>
+        <v>525</v>
       </c>
     </row>
     <row r="168">
@@ -5312,16 +5138,16 @@
         <v>11</v>
       </c>
       <c r="C168" t="s" s="0">
-        <v>552</v>
+        <v>526</v>
       </c>
       <c r="D168" t="s" s="0">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="E168" t="s" s="0">
-        <v>553</v>
+        <v>527</v>
       </c>
       <c r="F168" t="s" s="0">
-        <v>554</v>
+        <v>528</v>
       </c>
     </row>
     <row r="169">
@@ -5332,16 +5158,16 @@
         <v>11</v>
       </c>
       <c r="C169" t="s" s="0">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="D169" t="s" s="0">
-        <v>371</v>
+        <v>530</v>
       </c>
       <c r="E169" t="s" s="0">
-        <v>556</v>
+        <v>531</v>
       </c>
       <c r="F169" t="s" s="0">
-        <v>557</v>
+        <v>532</v>
       </c>
     </row>
     <row r="170">
@@ -5352,16 +5178,16 @@
         <v>11</v>
       </c>
       <c r="C170" t="s" s="0">
-        <v>558</v>
+        <v>533</v>
       </c>
       <c r="D170" t="s" s="0">
-        <v>165</v>
+        <v>534</v>
       </c>
       <c r="E170" t="s" s="0">
-        <v>22</v>
+        <v>535</v>
       </c>
       <c r="F170" t="s" s="0">
-        <v>559</v>
+        <v>536</v>
       </c>
     </row>
     <row r="171">
@@ -5372,16 +5198,16 @@
         <v>11</v>
       </c>
       <c r="C171" t="s" s="0">
-        <v>560</v>
+        <v>537</v>
       </c>
       <c r="D171" t="s" s="0">
-        <v>561</v>
+        <v>538</v>
       </c>
       <c r="E171" t="s" s="0">
-        <v>562</v>
+        <v>539</v>
       </c>
       <c r="F171" t="s" s="0">
-        <v>563</v>
+        <v>540</v>
       </c>
     </row>
     <row r="172">
@@ -5392,16 +5218,16 @@
         <v>11</v>
       </c>
       <c r="C172" t="s" s="0">
-        <v>564</v>
+        <v>541</v>
       </c>
       <c r="D172" t="s" s="0">
-        <v>565</v>
+        <v>19</v>
       </c>
       <c r="E172" t="s" s="0">
-        <v>566</v>
+        <v>542</v>
       </c>
       <c r="F172" t="s" s="0">
-        <v>567</v>
+        <v>197</v>
       </c>
     </row>
     <row r="173">
@@ -5412,16 +5238,16 @@
         <v>11</v>
       </c>
       <c r="C173" t="s" s="0">
-        <v>568</v>
+        <v>543</v>
       </c>
       <c r="D173" t="s" s="0">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="E173" t="s" s="0">
-        <v>569</v>
+        <v>544</v>
       </c>
       <c r="F173" t="s" s="0">
-        <v>570</v>
+        <v>545</v>
       </c>
     </row>
     <row r="174">
@@ -5432,16 +5258,16 @@
         <v>11</v>
       </c>
       <c r="C174" t="s" s="0">
-        <v>571</v>
+        <v>546</v>
       </c>
       <c r="D174" t="s" s="0">
-        <v>572</v>
+        <v>404</v>
       </c>
       <c r="E174" t="s" s="0">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="F174" t="s" s="0">
-        <v>574</v>
+        <v>548</v>
       </c>
     </row>
     <row r="175">
@@ -5452,16 +5278,16 @@
         <v>11</v>
       </c>
       <c r="C175" t="s" s="0">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="D175" t="s" s="0">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c r="E175" t="s" s="0">
-        <v>576</v>
+        <v>550</v>
       </c>
       <c r="F175" t="s" s="0">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="176">
@@ -5472,16 +5298,16 @@
         <v>11</v>
       </c>
       <c r="C176" t="s" s="0">
-        <v>577</v>
+        <v>551</v>
       </c>
       <c r="D176" t="s" s="0">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="E176" t="s" s="0">
-        <v>578</v>
+        <v>22</v>
       </c>
       <c r="F176" t="s" s="0">
-        <v>579</v>
+        <v>22</v>
       </c>
     </row>
     <row r="177">
@@ -5492,16 +5318,16 @@
         <v>11</v>
       </c>
       <c r="C177" t="s" s="0">
-        <v>580</v>
+        <v>552</v>
       </c>
       <c r="D177" t="s" s="0">
-        <v>366</v>
+        <v>553</v>
       </c>
       <c r="E177" t="s" s="0">
-        <v>581</v>
+        <v>22</v>
       </c>
       <c r="F177" t="s" s="0">
-        <v>582</v>
+        <v>554</v>
       </c>
     </row>
     <row r="178">
@@ -5512,16 +5338,16 @@
         <v>11</v>
       </c>
       <c r="C178" t="s" s="0">
-        <v>583</v>
+        <v>555</v>
       </c>
       <c r="D178" t="s" s="0">
-        <v>584</v>
+        <v>64</v>
       </c>
       <c r="E178" t="s" s="0">
-        <v>585</v>
+        <v>556</v>
       </c>
       <c r="F178" t="s" s="0">
-        <v>586</v>
+        <v>557</v>
       </c>
     </row>
     <row r="179">
@@ -5532,16 +5358,16 @@
         <v>11</v>
       </c>
       <c r="C179" t="s" s="0">
-        <v>587</v>
+        <v>558</v>
       </c>
       <c r="D179" t="s" s="0">
-        <v>588</v>
+        <v>559</v>
       </c>
       <c r="E179" t="s" s="0">
-        <v>589</v>
+        <v>560</v>
       </c>
       <c r="F179" t="s" s="0">
-        <v>590</v>
+        <v>561</v>
       </c>
     </row>
     <row r="180">
@@ -5552,16 +5378,16 @@
         <v>11</v>
       </c>
       <c r="C180" t="s" s="0">
-        <v>591</v>
+        <v>562</v>
       </c>
       <c r="D180" t="s" s="0">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="E180" t="s" s="0">
-        <v>592</v>
+        <v>563</v>
       </c>
       <c r="F180" t="s" s="0">
-        <v>593</v>
+        <v>564</v>
       </c>
     </row>
     <row r="181">
@@ -5572,16 +5398,16 @@
         <v>11</v>
       </c>
       <c r="C181" t="s" s="0">
-        <v>594</v>
+        <v>565</v>
       </c>
       <c r="D181" t="s" s="0">
-        <v>96</v>
+        <v>566</v>
       </c>
       <c r="E181" t="s" s="0">
-        <v>595</v>
+        <v>567</v>
       </c>
       <c r="F181" t="s" s="0">
-        <v>596</v>
+        <v>568</v>
       </c>
     </row>
     <row r="182">
@@ -5592,16 +5418,16 @@
         <v>11</v>
       </c>
       <c r="C182" t="s" s="0">
-        <v>597</v>
+        <v>569</v>
       </c>
       <c r="D182" t="s" s="0">
-        <v>446</v>
+        <v>570</v>
       </c>
       <c r="E182" t="s" s="0">
-        <v>598</v>
+        <v>571</v>
       </c>
       <c r="F182" t="s" s="0">
-        <v>599</v>
+        <v>572</v>
       </c>
     </row>
     <row r="183">
@@ -5612,196 +5438,16 @@
         <v>11</v>
       </c>
       <c r="C183" t="s" s="0">
-        <v>600</v>
+        <v>573</v>
       </c>
       <c r="D183" t="s" s="0">
-        <v>17</v>
+        <v>331</v>
       </c>
       <c r="E183" t="s" s="0">
-        <v>601</v>
+        <v>574</v>
       </c>
       <c r="F183" t="s" s="0">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n" s="0">
-        <v>182.0</v>
-      </c>
-      <c r="B184" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C184" t="s" s="0">
-        <v>603</v>
-      </c>
-      <c r="D184" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="E184" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="F184" t="s" s="0">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n" s="0">
-        <v>183.0</v>
-      </c>
-      <c r="B185" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C185" t="s" s="0">
-        <v>604</v>
-      </c>
-      <c r="D185" t="s" s="0">
-        <v>605</v>
-      </c>
-      <c r="E185" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="F185" t="s" s="0">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n" s="0">
-        <v>184.0</v>
-      </c>
-      <c r="B186" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C186" t="s" s="0">
-        <v>607</v>
-      </c>
-      <c r="D186" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="E186" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="F186" t="s" s="0">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n" s="0">
-        <v>185.0</v>
-      </c>
-      <c r="B187" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C187" t="s" s="0">
-        <v>609</v>
-      </c>
-      <c r="D187" t="s" s="0">
-        <v>610</v>
-      </c>
-      <c r="E187" t="s" s="0">
-        <v>611</v>
-      </c>
-      <c r="F187" t="s" s="0">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n" s="0">
-        <v>186.0</v>
-      </c>
-      <c r="B188" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C188" t="s" s="0">
-        <v>613</v>
-      </c>
-      <c r="D188" t="s" s="0">
-        <v>614</v>
-      </c>
-      <c r="E188" t="s" s="0">
-        <v>615</v>
-      </c>
-      <c r="F188" t="s" s="0">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n" s="0">
-        <v>187.0</v>
-      </c>
-      <c r="B189" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C189" t="s" s="0">
-        <v>617</v>
-      </c>
-      <c r="D189" t="s" s="0">
-        <v>618</v>
-      </c>
-      <c r="E189" t="s" s="0">
-        <v>619</v>
-      </c>
-      <c r="F189" t="s" s="0">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n" s="0">
-        <v>188.0</v>
-      </c>
-      <c r="B190" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C190" t="s" s="0">
-        <v>621</v>
-      </c>
-      <c r="D190" t="s" s="0">
-        <v>622</v>
-      </c>
-      <c r="E190" t="s" s="0">
-        <v>623</v>
-      </c>
-      <c r="F190" t="s" s="0">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n" s="0">
-        <v>189.0</v>
-      </c>
-      <c r="B191" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C191" t="s" s="0">
-        <v>625</v>
-      </c>
-      <c r="D191" t="s" s="0">
-        <v>626</v>
-      </c>
-      <c r="E191" t="s" s="0">
-        <v>627</v>
-      </c>
-      <c r="F191" t="s" s="0">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n" s="0">
-        <v>190.0</v>
-      </c>
-      <c r="B192" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C192" t="s" s="0">
-        <v>629</v>
-      </c>
-      <c r="D192" t="s" s="0">
-        <v>630</v>
-      </c>
-      <c r="E192" t="s" s="0">
-        <v>631</v>
-      </c>
-      <c r="F192" t="s" s="0">
-        <v>632</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
